--- a/artfynd/A 12986-2024 artfynd.xlsx
+++ b/artfynd/A 12986-2024 artfynd.xlsx
@@ -2110,7 +2110,7 @@
         <v>116869539</v>
       </c>
       <c r="B16" t="n">
-        <v>57278</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>116869867</v>
       </c>
       <c r="B85" t="n">
-        <v>57278</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>

--- a/artfynd/A 12986-2024 artfynd.xlsx
+++ b/artfynd/A 12986-2024 artfynd.xlsx
@@ -2110,7 +2110,7 @@
         <v>116869539</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>116869867</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
